--- a/import/schedule/Расписание-1 .xlsx
+++ b/import/schedule/Расписание-1 .xlsx
@@ -14324,97 +14324,85 @@
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
     </font>
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
       <charset val="204"/>
-      <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
       <charset val="204"/>
-      <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
       <charset val="204"/>
-      <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
       <charset val="204"/>
-      <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
       <charset val="204"/>
-      <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
       <charset val="204"/>
-      <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
       <charset val="204"/>
-      <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
       <charset val="204"/>
-      <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
       <charset val="204"/>
-      <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
       <charset val="204"/>
-      <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
       <charset val="204"/>
-      <scheme val="minor"/>
     </font>
     <font>
       <sz val="12"/>
@@ -14477,10 +14465,9 @@
       <b/>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
       <charset val="204"/>
-      <scheme val="minor"/>
     </font>
     <font>
       <b/>
@@ -14532,10 +14519,9 @@
       <i/>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
       <charset val="204"/>
-      <scheme val="minor"/>
     </font>
     <font>
       <b/>
@@ -14557,10 +14543,9 @@
       <u/>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
       <charset val="204"/>
-      <scheme val="minor"/>
     </font>
     <font>
       <b/>
@@ -14595,9 +14580,8 @@
     <font>
       <sz val="55"/>
       <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
     </font>
     <font>
       <b/>
@@ -14621,10 +14605,9 @@
       <b/>
       <sz val="48"/>
       <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
       <charset val="204"/>
-      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="3">
@@ -16171,7 +16154,7 @@
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
+        <a:latin typeface="Times New Roman" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="Yu Gothic Light"/>
@@ -16206,7 +16189,7 @@
         <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+        <a:latin typeface="Times New Roman" panose="020F0502020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="Yu Gothic"/>
